--- a/data/S2011_12_FINAL.xlsx
+++ b/data/S2011_12_FINAL.xlsx
@@ -27,8 +27,11 @@
     <sheet name="SERIES" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="CLUBS" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="META" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$7</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -36,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,8 +54,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +76,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -82,11 +94,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -11725,7 +11743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11769,6 +11787,93 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2011_12_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2011_12_0030 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2011_12_0031 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0021</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2011_12_0021 'Baráž o Extraligu' (L15, parent=NODE_S2011_12_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0028</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2011_12_0028 'Baráž o I.ligu' (L25, parent=NODE_S2011_12_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0042</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2011_12_0042 'O postup do I.ligy' (L15, parent=NODE_S2011_12_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -15393,8 +15498,6 @@
         </is>
       </c>
     </row>
-    <row r="87"/>
-    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
@@ -15474,7 +15577,6 @@
         </is>
       </c>
     </row>
-    <row r="96"/>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
@@ -31174,6 +31276,193 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0029</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0030</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0030 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0031</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0031 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0021</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2011_12_0021 'Baráž o Extraligu' (L15, parent=NODE_S2011_12_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0028</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2011_12_0028 'Baráž o I.ligu' (L25, parent=NODE_S2011_12_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0042</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2011_12_0042 'O postup do I.ligy' (L15, parent=NODE_S2011_12_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S2011_12_FINAL.xlsx
+++ b/data/S2011_12_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -9104,6 +9104,11 @@
           <t>CLUB_S2010_11_0239</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>sestup</t>
+        </is>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>TR_S2011_12_00268</t>
@@ -11743,7 +11748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11793,7 +11798,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2011_12_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -11805,7 +11810,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2011_12_0030 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -11817,7 +11822,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2011_12_0031 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -11827,14 +11832,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NODE_S2011_12_0021</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2011_12_0021 'Baráž o Extraligu' (L15, parent=NODE_S2011_12_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -11844,14 +11844,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NODE_S2011_12_0028</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2011_12_0028 'Baráž o I.ligu' (L25, parent=NODE_S2011_12_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -11861,17 +11856,447 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NODE_S2011_12_0042</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2011_12_0042 'O postup do I.ligy' (L15, parent=NODE_S2011_12_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2010_11_0252 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SKP Rapid Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Závodní hokejové Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HCM Warrior Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0030</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina A'</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0031</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina B'</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0032</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina C'</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -15498,6 +15923,8 @@
         </is>
       </c>
     </row>
+    <row r="87"/>
+    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
@@ -15528,6 +15955,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0001</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -15540,6 +15972,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0003</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -15552,6 +15989,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0003</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -15564,6 +16006,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0036</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -15577,6 +16024,7 @@
         </is>
       </c>
     </row>
+    <row r="96"/>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
@@ -18986,12 +19434,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -19196,12 +19644,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -19364,12 +19812,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -19448,12 +19896,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov.</t>
+          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov. || TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>KLH VT VTJ Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -19574,12 +20022,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -19784,12 +20232,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Kadaň = Sportovní klub Kadaň (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj (okres Chomutov). city Kadaň.</t>
+          <t>Kadaň = Sportovní klub Kadaň (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj (okres Chomutov). city Kadaň. || TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Sportovní klub Kadaň</t>
+          <t>Kadaň</t>
         </is>
       </c>
     </row>
@@ -20088,12 +20536,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -20236,12 +20684,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Slaný = UHK LEV Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). **UHK** = Univerzitni hokejovy klub. Patterns: HK Lev Slaný. city Slaný.</t>
+          <t>Slaný = UHK LEV Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). **UHK** = Univerzitni hokejovy klub. Patterns: HK Lev Slaný. city Slaný. || TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>UHK LEV Slaný</t>
+          <t>Slaný</t>
         </is>
       </c>
     </row>
@@ -20384,12 +20832,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>Moravské Budějovice</t>
         </is>
       </c>
     </row>
@@ -20799,12 +21247,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou.</t>
+          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou. || TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Vlci Jablonec nad Nisou</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -20841,12 +21289,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Klatovy = SHC Maso Brejcha Klatovy (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. **Maso Brejcha** = sponzor (řeznictví). city Klatovy.</t>
+          <t>Klatovy = SHC Maso Brejcha Klatovy (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. **Maso Brejcha** = sponzor (řeznictví). city Klatovy. || TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>SHC Maso Brejcha Klatovy</t>
+          <t>Klatovy</t>
         </is>
       </c>
     </row>
@@ -21014,12 +21462,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Brno = VSK Technika Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VSK Technika** = Vysokoškolský sportovní klub (VUT Brno). city Brno.</t>
+          <t>Brno = VSK Technika Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VSK Technika** = Vysokoškolský sportovní klub (VUT Brno). city Brno. || TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>VSK Technika Brno</t>
+          <t>Technika Brno</t>
         </is>
       </c>
     </row>
@@ -21098,12 +21546,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Nymburk = NED Hockey Nymburk (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Post-revolucni. city Nymburk.</t>
+          <t>Nymburk = NED Hockey Nymburk (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Post-revolucni. city Nymburk. || TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>NED Hockey Nymburk</t>
+          <t>Nymburk</t>
         </is>
       </c>
     </row>
@@ -21140,12 +21588,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -21182,12 +21630,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>SC Kolín</t>
         </is>
       </c>
     </row>
@@ -21817,12 +22265,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Ostrava (Poruba) = HC RT Torax Poruba (Wiki D42 - registr ustavy 04/2026). Moravskoslezsky kraj. **RT Torax** = sponzor (medical device firma). Patterns: HK Poruba. city Ostrava (Poruba).</t>
+          <t>Ostrava (Poruba) = HC RT Torax Poruba (Wiki D42 - registr ustavy 04/2026). Moravskoslezsky kraj. **RT Torax** = sponzor (medical device firma). Patterns: HK Poruba. city Ostrava (Poruba). || TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>RT Torax Poruba</t>
+          <t>Poruba</t>
         </is>
       </c>
     </row>
@@ -21943,12 +22391,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Slaný = UHK LEV Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). **UHK** = Univerzitni hokejovy klub. Patterns: HK Lev Slaný. city Slaný.</t>
+          <t>Slaný = UHK LEV Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). **UHK** = Univerzitni hokejovy klub. Patterns: HK Lev Slaný. city Slaný. || TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>UHK LEV Slaný</t>
+          <t>Slaný</t>
         </is>
       </c>
     </row>
@@ -22237,12 +22685,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -22840,12 +23288,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -22924,12 +23372,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -23428,12 +23876,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Plzeň = HC Ekonomické Stavby Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. city Plzeň.</t>
+          <t>Plzeň = HC Ekonomické Stavby Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. city Plzeň. || TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Ekonomické Stavby Plzeň</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -24394,12 +24842,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Plzeň = SKP Rapid Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. **SKP** = Sportovni klub policie. city Plzeň.</t>
+          <t>Plzeň = SKP Rapid Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. **SKP** = Sportovni klub policie. city Plzeň. || TBD: city 'SKP Rapid Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>SKP Rapid Plzeň</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -24767,12 +25215,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Plzeň = HC Ekonomické Stavby Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. city Plzeň.</t>
+          <t>Plzeň = HC Ekonomické Stavby Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. city Plzeň. || TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Ekonomické Stavby Plzeň</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -25832,12 +26280,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Cheb = PSK 96 Cheb (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj. **PSK 96** = Policejni sportovni klub zalozen 1996. city Cheb.</t>
+          <t>Cheb = PSK 96 Cheb (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj. **PSK 96** = Policejni sportovni klub zalozen 1996. city Cheb. || TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>PSK 96 Cheb</t>
+          <t>Cheb</t>
         </is>
       </c>
     </row>
@@ -25916,12 +26364,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Cheb = IHT Brimstones Cheb (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj. Post-revolucni anglicky nazev. city Cheb.</t>
+          <t>Cheb = IHT Brimstones Cheb (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj. Post-revolucni anglicky nazev. city Cheb. || TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>IHT Brimstones Cheb</t>
+          <t>Cheb</t>
         </is>
       </c>
     </row>
@@ -26551,12 +26999,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov.</t>
+          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov. || TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Stadion Nový Bydžov</t>
+          <t>Nový Bydžov</t>
         </is>
       </c>
     </row>
@@ -26635,12 +27083,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Nová Paka = BK JTC Nová Paka (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Jicin). **BK JTC** = Bruslarsky klub Jicinske telovychovne centrum. city Nová Paka.</t>
+          <t>Nová Paka = BK JTC Nová Paka (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Jicin). **BK JTC** = Bruslarsky klub Jicinske telovychovne centrum. city Nová Paka. || TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>BK JTC Nová Paka</t>
+          <t>Nová Paka</t>
         </is>
       </c>
     </row>
@@ -27065,12 +27513,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Pardubice = HC Závodní hokejové Pardubice (Wiki D42 - registr ustavy 04/2026). Pardubicky kraj. **Závodní hokejová liga**. city Pardubice.</t>
+          <t>Pardubice = HC Závodní hokejové Pardubice (Wiki D42 - registr ustavy 04/2026). Pardubicky kraj. **Závodní hokejová liga**. city Pardubice. || TBD: city 'Závodní hokejové Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Závodní hokejové Pardubice</t>
+          <t>Pardubice</t>
         </is>
       </c>
     </row>
@@ -27552,12 +28000,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>Moravské Budějovice</t>
         </is>
       </c>
     </row>
@@ -27799,12 +28247,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Brno = HCM Warrior Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **HCM** = post-revolucni klub. city Brno.</t>
+          <t>Brno = HCM Warrior Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **HCM** = post-revolucni klub. city Brno. || TBD: city 'HCM Warrior Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>HCM Warrior Brno</t>
+          <t>Brno</t>
         </is>
       </c>
     </row>
@@ -28229,12 +28677,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Rožnov pod Radhoštěm</t>
         </is>
       </c>
     </row>
@@ -28434,12 +28882,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Rožnov pod Radhoštěm</t>
         </is>
       </c>
     </row>
@@ -31282,11 +31730,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -31331,21 +31779,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0029</t>
+          <t>CLUB_S2011_12_0005</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -31353,21 +31799,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0030</t>
+          <t>CLUB_S2011_12_0010</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0030 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -31375,21 +31819,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0031</t>
+          <t>CLUB_S2011_12_0014</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0031 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -31397,21 +31839,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NODE_S2011_12_0021</t>
+          <t>CLUB_S2011_12_0016</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2011_12_0021 'Baráž o Extraligu' (L15, parent=NODE_S2011_12_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -31419,21 +31859,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NODE_S2011_12_0028</t>
+          <t>CLUB_S2011_12_0019</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2011_12_0028 'Baráž o I.ligu' (L25, parent=NODE_S2011_12_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -31441,24 +31879,722 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NODE_S2011_12_0042</t>
+          <t>CLUB_S2011_12_0024</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2011_12_0042 'O postup do I.ligy' (L15, parent=NODE_S2011_12_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0031</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0035</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0039</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0050</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0051</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0056</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0058</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0059</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0060</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0067</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2010_11_0252 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0076</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0079</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0086</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0100</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0102</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0102</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0114</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0139</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'SKP Rapid Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0148</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0162</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0175</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0177</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0188</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0193</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0195</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0203</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0206</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Závodní hokejové Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0210</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0219</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0225</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'HCM Warrior Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0237</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0242</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0030</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0031</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina B'</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0032</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina C'</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F7"/>
+  <autoFilter ref="A1:F42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S2011_12_FINAL.xlsx
+++ b/data/S2011_12_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -11748,7 +11748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11798,7 +11798,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -11810,7 +11810,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -11822,7 +11822,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -11834,7 +11834,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -11846,7 +11846,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -11858,7 +11858,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -11870,7 +11870,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -11882,7 +11882,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -11894,7 +11894,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -11906,7 +11906,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -11918,7 +11918,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2010_11_0252 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -11930,7 +11930,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -11942,7 +11942,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -11954,7 +11954,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -11966,7 +11966,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -11978,7 +11978,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2010_11_0252 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SKP Rapid Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -11990,7 +11990,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -12002,7 +12002,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -12014,7 +12014,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -12026,7 +12026,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -12038,7 +12038,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -12050,7 +12050,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -12062,7 +12062,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -12074,7 +12074,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SKP Rapid Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -12086,7 +12086,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Závodní hokejové Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -12098,7 +12098,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -12110,7 +12110,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HCM Warrior Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -12120,9 +12120,14 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0030</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina A'</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -12132,9 +12137,14 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0031</t>
+        </is>
+      </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina B'</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -12144,159 +12154,17 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0032</t>
+        </is>
+      </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina C'</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Závodní hokejové Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'HCM Warrior Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>NODE_S2011_12_0030</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina A'</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>NODE_S2011_12_0031</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina B'</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>NODE_S2011_12_0032</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Skupina C'</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -12313,7 +12181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K100"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12372,6 +12240,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12414,6 +12287,11 @@
           <t>14 týmů (5 stat sloupců): základ + QF/SF/finále + baráž. Mistr: HC ČSOB Pojišťovna Pardubice.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12461,6 +12339,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12503,6 +12386,11 @@
           <t>I.ČNHL: základ + playoff (QF/SF/finále/O 3.) + O 5.-8. + o udržení. I.SNHL (12). Kval o I.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12545,6 +12433,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12587,6 +12480,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12629,6 +12527,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12671,6 +12574,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12713,6 +12621,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12755,6 +12668,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12797,6 +12715,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12839,6 +12762,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12881,6 +12809,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12923,6 +12856,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12965,6 +12903,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13007,6 +12950,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13049,6 +12997,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13091,6 +13044,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13133,6 +13091,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -13175,6 +13138,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -13217,6 +13185,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -13259,6 +13232,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -13301,6 +13279,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -13343,6 +13326,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -13385,6 +13373,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -13427,6 +13420,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -13469,6 +13467,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -13511,6 +13514,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -13553,6 +13561,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0028</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -13600,6 +13613,11 @@
           <t>Kvalifikace o postup do II.ligy</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0029</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -13632,6 +13650,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0030</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -13664,6 +13687,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0031</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -13696,6 +13724,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0032</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -13738,6 +13771,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0033</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -13864,6 +13902,11 @@
           <t>II.liga: 2 skupiny + finále + o postup do I.ligy.</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0037</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -13906,6 +13949,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0038</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -13948,6 +13996,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0039</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -13990,6 +14043,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0040</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -14032,6 +14090,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0041</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -14074,6 +14137,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0042</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -14158,6 +14226,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0044</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -14200,6 +14273,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0045</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -14242,6 +14320,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0046</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -14284,6 +14367,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0047</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -14326,6 +14414,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0048</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -14368,6 +14461,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0049</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -14410,6 +14508,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0050</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -14452,6 +14555,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0051</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -14494,6 +14602,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0052</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -14536,6 +14649,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0053</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -14578,6 +14696,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0054</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -14620,6 +14743,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0055</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -14662,6 +14790,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0056</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -14746,6 +14879,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0057</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -14830,6 +14968,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0058</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -15166,6 +15309,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0063</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -15208,6 +15356,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0068</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -15250,6 +15403,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0069</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -15292,6 +15450,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0070</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -15334,6 +15497,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0071</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -15376,6 +15544,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0073</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -15628,6 +15801,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0078</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -15670,6 +15848,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0079</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -15712,6 +15895,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0080</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -15836,6 +16024,11 @@
       <c r="K84" t="inlineStr">
         <is>
           <t>Kontejner L40</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>NODE_S2010_11_0083</t>
         </is>
       </c>
     </row>
@@ -15943,6 +16136,11 @@
           <t>I.liga (10 týmů, jeden stůl)</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -15960,6 +16158,11 @@
           <t>NODE_S2011_12_0001</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -15977,6 +16180,11 @@
           <t>NODE_S2011_12_0003</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -15994,6 +16202,11 @@
           <t>NODE_S2011_12_0003</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -16011,6 +16224,11 @@
           <t>NODE_S2011_12_0036</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -16021,6 +16239,11 @@
       <c r="B95" t="inlineStr">
         <is>
           <t>Okresní přebory (jen registr)</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>okresní</t>
         </is>
       </c>
     </row>
@@ -19434,12 +19657,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -19812,12 +20035,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -20022,12 +20245,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -20832,12 +21055,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Moravské Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -21630,12 +21853,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>SC Kolín</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -22685,12 +22908,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -23288,12 +23511,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -23372,12 +23595,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -28000,12 +28223,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>Moravské Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -28677,12 +28900,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Rožnov pod Radhoštěm</t>
+          <t>Havlíčkův Brod</t>
         </is>
       </c>
     </row>
@@ -28882,12 +29105,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>Rožnov pod Radhoštěm</t>
+          <t>Havlíčkův Brod</t>
         </is>
       </c>
     </row>
@@ -31730,7 +31953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -31784,12 +32007,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0005</t>
+          <t>CLUB_S2011_12_0010</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -31804,12 +32027,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0010</t>
+          <t>CLUB_S2011_12_0016</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -31824,12 +32047,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0014</t>
+          <t>CLUB_S2011_12_0024</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -31844,12 +32067,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0016</t>
+          <t>CLUB_S2011_12_0031</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -31864,12 +32087,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0019</t>
+          <t>CLUB_S2011_12_0035</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -31884,12 +32107,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0024</t>
+          <t>CLUB_S2011_12_0050</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -31904,12 +32127,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0031</t>
+          <t>CLUB_S2011_12_0051</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -31924,12 +32147,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0035</t>
+          <t>CLUB_S2011_12_0056</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -31944,12 +32167,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0039</t>
+          <t>CLUB_S2011_12_0058</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -31964,12 +32187,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0050</t>
+          <t>CLUB_S2011_12_0059</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -31984,12 +32207,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0051</t>
+          <t>CLUB_S2011_12_0067</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2010_11_0252 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -32004,12 +32227,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0056</t>
+          <t>CLUB_S2011_12_0076</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -32024,12 +32247,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0058</t>
+          <t>CLUB_S2011_12_0079</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -32044,12 +32267,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0059</t>
+          <t>CLUB_S2011_12_0102</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -32064,12 +32287,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0060</t>
+          <t>CLUB_S2011_12_0114</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -32084,12 +32307,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0067</t>
+          <t>CLUB_S2011_12_0139</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S2010_11_0252 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'SKP Rapid Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -32104,12 +32327,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0076</t>
+          <t>CLUB_S2011_12_0148</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -32124,12 +32347,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0079</t>
+          <t>CLUB_S2011_12_0162</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -32144,12 +32367,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0086</t>
+          <t>CLUB_S2011_12_0175</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -32164,12 +32387,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0100</t>
+          <t>CLUB_S2011_12_0177</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -32184,12 +32407,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0102</t>
+          <t>CLUB_S2011_12_0188</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -32204,12 +32427,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0102</t>
+          <t>CLUB_S2011_12_0193</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -32224,12 +32447,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0114</t>
+          <t>CLUB_S2011_12_0195</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -32244,12 +32467,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0139</t>
+          <t>CLUB_S2011_12_0203</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'SKP Rapid Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -32264,12 +32487,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0148</t>
+          <t>CLUB_S2011_12_0206</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Závodní hokejové Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -32284,12 +32507,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0162</t>
+          <t>CLUB_S2011_12_0210</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
     </row>
@@ -32304,12 +32527,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0175</t>
+          <t>CLUB_S2011_12_0225</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'HCM Warrior Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -32319,17 +32542,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0177</t>
+          <t>NODE_S2011_12_0030</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina A'</t>
         </is>
       </c>
     </row>
@@ -32339,17 +32562,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0188</t>
+          <t>NODE_S2011_12_0031</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina B'</t>
         </is>
       </c>
     </row>
@@ -32359,242 +32582,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S2011_12_0193</t>
+          <t>NODE_S2011_12_0032</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>CLUB_S2011_12_0195</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>CLUB_S2011_12_0203</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>CLUB_S2011_12_0206</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Závodní hokejové Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>CLUB_S2011_12_0210</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>CLUB_S2011_12_0219</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>CLUB_S2011_12_0225</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'HCM Warrior Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>CLUB_S2011_12_0237</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>CLUB_S2011_12_0242</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>NODE_S2011_12_0030</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina A'</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>NODE_S2011_12_0031</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina B'</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>NODE_S2011_12_0032</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina C'</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F42"/>
+  <autoFilter ref="A1:F31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S2011_12_FINAL.xlsx
+++ b/data/S2011_12_FINAL.xlsx
@@ -12181,7 +12181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:N100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12245,6 +12245,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16116,8 +16126,6 @@
         </is>
       </c>
     </row>
-    <row r="87"/>
-    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
@@ -16247,7 +16255,6 @@
         </is>
       </c>
     </row>
-    <row r="96"/>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>

--- a/data/S2011_12_FINAL.xlsx
+++ b/data/S2011_12_FINAL.xlsx
@@ -12433,6 +12433,16 @@
           <t>NODE_S2011_12_0001</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0010</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0016</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12447,6 +12457,14 @@
         <is>
           <t>NODE_S2010_11_0004</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -12621,6 +12639,16 @@
           <t>NODE_S2011_12_0007</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0010</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0019</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12635,6 +12663,14 @@
         <is>
           <t>NODE_S2010_11_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -12715,6 +12751,16 @@
           <t>NODE_S2011_12_0007</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0011</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0019</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12729,6 +12775,14 @@
         <is>
           <t>NODE_S2010_11_0010</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -12762,6 +12816,16 @@
           <t>NODE_S2011_12_0007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0015</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0014</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12776,6 +12840,14 @@
         <is>
           <t>NODE_S2010_11_0011</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -12809,6 +12881,8 @@
           <t>NODE_S2011_12_0007</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12823,6 +12897,14 @@
         <is>
           <t>NODE_S2010_11_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -12856,6 +12938,8 @@
           <t>NODE_S2011_12_0007</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12870,6 +12954,14 @@
         <is>
           <t>NODE_S2010_11_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -12903,6 +12995,8 @@
           <t>NODE_S2011_12_0007</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12917,6 +13011,14 @@
         <is>
           <t>NODE_S2010_11_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -12950,6 +13052,8 @@
           <t>NODE_S2011_12_0007</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12964,6 +13068,14 @@
         <is>
           <t>NODE_S2010_11_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -12997,6 +13109,8 @@
           <t>NODE_S2011_12_0001</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13011,6 +13125,14 @@
         <is>
           <t>NODE_S2010_11_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -13044,6 +13166,8 @@
           <t>NODE_S2011_12_0007</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13058,6 +13182,14 @@
         <is>
           <t>NODE_S2010_11_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -13091,6 +13223,8 @@
           <t>NODE_S2011_12_0007</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13105,6 +13239,14 @@
         <is>
           <t>NODE_S2010_11_0018</t>
         </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -13138,6 +13280,16 @@
           <t>NODE_S2011_12_0007</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0013</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0012</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13152,6 +13304,14 @@
         <is>
           <t>NODE_S2010_11_0019</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -13279,6 +13439,16 @@
           <t>NODE_S2011_12_0003</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0023</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0027</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13293,6 +13463,14 @@
         <is>
           <t>NODE_S2010_11_0022</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -13326,6 +13504,16 @@
           <t>NODE_S2011_12_0003</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0024</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0027</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13340,6 +13528,14 @@
         <is>
           <t>NODE_S2010_11_0023</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -13373,6 +13569,12 @@
           <t>NODE_S2011_12_0003</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13387,6 +13589,14 @@
         <is>
           <t>NODE_S2010_11_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -13420,6 +13630,12 @@
           <t>NODE_S2011_12_0003</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13434,6 +13650,14 @@
         <is>
           <t>NODE_S2010_11_0025</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -13467,6 +13691,8 @@
           <t>NODE_S2011_12_0003</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13481,6 +13707,14 @@
         <is>
           <t>NODE_S2010_11_0026</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -13514,6 +13748,8 @@
           <t>NODE_S2011_12_0003</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13528,6 +13764,14 @@
         <is>
           <t>NODE_S2010_11_0027</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>10.–14. ZČ</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -14043,6 +14287,12 @@
           <t>NODE_S2011_12_0036</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0040</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14057,6 +14307,14 @@
         <is>
           <t>NODE_S2010_11_0040</t>
         </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -14090,6 +14348,12 @@
           <t>NODE_S2011_12_0036</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0041</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14104,6 +14368,14 @@
         <is>
           <t>NODE_S2010_11_0041</t>
         </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -14137,6 +14409,8 @@
           <t>NODE_S2011_12_0036</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14151,6 +14425,14 @@
         <is>
           <t>NODE_S2010_11_0042</t>
         </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -14273,6 +14555,8 @@
           <t>NODE_S2011_12_0036</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14287,6 +14571,14 @@
         <is>
           <t>NODE_S2010_11_0045</t>
         </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -14414,6 +14706,12 @@
           <t>NODE_S2011_12_0036</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0039</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14428,6 +14726,14 @@
         <is>
           <t>NODE_S2010_11_0048</t>
         </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -14508,6 +14814,12 @@
           <t>NODE_S2011_12_0048</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0050</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14522,6 +14834,14 @@
         <is>
           <t>NODE_S2010_11_0050</t>
         </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -14555,6 +14875,8 @@
           <t>NODE_S2011_12_0048</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14569,6 +14891,14 @@
         <is>
           <t>NODE_S2010_11_0051</t>
         </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="52">
@@ -14649,6 +14979,12 @@
           <t>NODE_S2011_12_0051</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0053</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14663,6 +14999,14 @@
         <is>
           <t>NODE_S2010_11_0053</t>
         </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -14696,6 +15040,8 @@
           <t>NODE_S2011_12_0051</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14710,6 +15056,14 @@
         <is>
           <t>NODE_S2010_11_0054</t>
         </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -14738,6 +15092,12 @@
           <t>REG_PLK</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0056</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14757,6 +15117,14 @@
         <is>
           <t>NODE_S2010_11_0055</t>
         </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>9 týmů</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -14837,6 +15205,8 @@
           <t>NODE_S2011_12_0054</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14846,6 +15216,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="58">
@@ -14926,6 +15304,8 @@
           <t>NODE_S2011_12_0054</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14935,6 +15315,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -15015,6 +15403,8 @@
           <t>NODE_S2011_12_0054</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15024,6 +15414,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="62">
@@ -15099,6 +15497,8 @@
           <t>NODE_S2011_12_0054</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15108,6 +15508,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -15183,6 +15591,12 @@
           <t>NODE_S2011_12_0063</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0066</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15192,6 +15606,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -15225,6 +15647,12 @@
           <t>NODE_S2011_12_0063</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0066</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15234,6 +15662,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -15267,6 +15703,8 @@
           <t>NODE_S2011_12_0063</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15276,6 +15714,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="68">
@@ -15591,6 +16037,12 @@
           <t>NODE_S2011_12_0072</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0075</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15600,6 +16052,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>11 týmů</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -15675,6 +16135,8 @@
           <t>NODE_S2011_12_0072</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15684,6 +16146,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="77">
@@ -15759,6 +16229,8 @@
           <t>NODE_S2011_12_0072</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15768,6 +16240,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -15895,6 +16375,12 @@
           <t>NODE_S2011_12_0079</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0081</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15909,6 +16395,14 @@
         <is>
           <t>NODE_S2010_11_0080</t>
         </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -15942,6 +16436,8 @@
           <t>NODE_S2011_12_0079</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15951,6 +16447,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -15984,6 +16488,8 @@
           <t>NODE_S2011_12_0079</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15993,6 +16499,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="84">
@@ -16073,6 +16587,12 @@
           <t>NODE_S2011_12_0083</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0085</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16082,6 +16602,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -16115,6 +16643,8 @@
           <t>NODE_S2011_12_0083</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16125,7 +16655,17 @@
           <t>complete</t>
         </is>
       </c>
-    </row>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87"/>
+    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
@@ -16255,6 +16795,7 @@
         </is>
       </c>
     </row>
+    <row r="96"/>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>

--- a/data/S2011_12_FINAL.xlsx
+++ b/data/S2011_12_FINAL.xlsx
@@ -910,6 +910,11 @@
           <t>HC ČSOB Pojišťovna Pardubice</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F7" t="n">
         <v>52</v>
       </c>
@@ -12881,8 +12886,6 @@
           <t>NODE_S2011_12_0007</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12938,8 +12941,6 @@
           <t>NODE_S2011_12_0007</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12995,8 +12996,6 @@
           <t>NODE_S2011_12_0007</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13052,8 +13051,6 @@
           <t>NODE_S2011_12_0007</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13109,8 +13106,6 @@
           <t>NODE_S2011_12_0001</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13166,8 +13161,6 @@
           <t>NODE_S2011_12_0007</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13223,8 +13216,6 @@
           <t>NODE_S2011_12_0007</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13574,7 +13565,6 @@
           <t>NODE_S2011_12_0025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13635,7 +13625,6 @@
           <t>NODE_S2011_12_0026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13691,8 +13680,6 @@
           <t>NODE_S2011_12_0003</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13748,8 +13735,6 @@
           <t>NODE_S2011_12_0003</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14292,7 +14277,6 @@
           <t>NODE_S2011_12_0040</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14353,7 +14337,6 @@
           <t>NODE_S2011_12_0041</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14409,8 +14392,6 @@
           <t>NODE_S2011_12_0036</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14555,8 +14536,6 @@
           <t>NODE_S2011_12_0036</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14711,7 +14690,6 @@
           <t>NODE_S2011_12_0039</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14819,7 +14797,6 @@
           <t>NODE_S2011_12_0050</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14875,8 +14852,6 @@
           <t>NODE_S2011_12_0048</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14984,7 +14959,6 @@
           <t>NODE_S2011_12_0053</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15040,8 +15014,6 @@
           <t>NODE_S2011_12_0051</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15097,7 +15069,6 @@
           <t>NODE_S2011_12_0056</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15205,8 +15176,6 @@
           <t>NODE_S2011_12_0054</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15304,8 +15273,6 @@
           <t>NODE_S2011_12_0054</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15403,8 +15370,6 @@
           <t>NODE_S2011_12_0054</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15497,8 +15462,6 @@
           <t>NODE_S2011_12_0054</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15596,7 +15559,6 @@
           <t>NODE_S2011_12_0066</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15652,7 +15614,6 @@
           <t>NODE_S2011_12_0066</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15703,8 +15664,6 @@
           <t>NODE_S2011_12_0063</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16042,7 +16001,6 @@
           <t>NODE_S2011_12_0075</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16135,8 +16093,6 @@
           <t>NODE_S2011_12_0072</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16229,8 +16185,6 @@
           <t>NODE_S2011_12_0072</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16380,7 +16334,6 @@
           <t>NODE_S2011_12_0081</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16436,8 +16389,6 @@
           <t>NODE_S2011_12_0079</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16488,8 +16439,6 @@
           <t>NODE_S2011_12_0079</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16592,7 +16541,6 @@
           <t>NODE_S2011_12_0085</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16643,8 +16591,6 @@
           <t>NODE_S2011_12_0083</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16664,8 +16610,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87"/>
-    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
@@ -16795,7 +16739,6 @@
         </is>
       </c>
     </row>
-    <row r="96"/>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
@@ -32259,7 +32202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32487,6 +32430,18 @@
       <c r="B19" t="inlineStr">
         <is>
           <t>0 oprav kvalifikačních levelů. Sloupec Q (level) aktualizován.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HC ČSOB Pojišťovna Pardubice</t>
         </is>
       </c>
     </row>

--- a/data/S2011_12_FINAL.xlsx
+++ b/data/S2011_12_FINAL.xlsx
@@ -16610,6 +16610,8 @@
         <v>5</v>
       </c>
     </row>
+    <row r="87"/>
+    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
@@ -16739,6 +16741,7 @@
         </is>
       </c>
     </row>
+    <row r="96"/>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>

--- a/data/S2011_12_FINAL.xlsx
+++ b/data/S2011_12_FINAL.xlsx
@@ -2687,7 +2687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3266,6 +3266,115 @@
       <c r="U8" s="2" t="n"/>
       <c r="V8" s="2" t="n"/>
       <c r="W8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0086</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TJ Bohemians Praha</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0086</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0243</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>TR_S2011_12_00290</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HC Predators Česká Lípa</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0086</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0244</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>TR_S2011_12_00291</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7997,7 +8106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:W29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -8645,6 +8754,883 @@
       <c r="V9" t="inlineStr">
         <is>
           <t>TR_S2011_12_00265</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0087</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HPH Pokojovice</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0087</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0245</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>TR_S2011_12_00292</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sokol OKŘÍŠKY</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0087</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0246</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>TR_S2011_12_00293</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HC LUKÁŠ B</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0087</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0247</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>TR_S2011_12_00294</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Veselý TEAM</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0087</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0248</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>TR_S2011_12_00295</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>KRHOV</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0087</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0249</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>TR_S2011_12_00296</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>HC LUKÁŠ A</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0087</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0250</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>TR_S2011_12_00297</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>7</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TJ Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0087</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0251</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>TR_S2011_12_00298</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Hokejový klub – Drakstav</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0087</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0252</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>TR_S2011_12_00299</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HC Drakstav</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0087</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0253</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>TR_S2011_12_00300</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MÁ Jihlava</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0087</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0254</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>TR_S2011_12_00301</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HC Rantířov</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0087</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0255</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>TR_S2011_12_00302</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0087</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0256</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>TR_S2011_12_00303</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0087</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0257</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>TR_S2011_12_00304</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HC Janovice</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0087</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0258</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>TR_S2011_12_00305</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>6</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HC Fan Club Dukla Jihlava</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0087</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0259</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>TR_S2011_12_00306</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>7</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice-Brod</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0087</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0260</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>TR_S2011_12_00307</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>8</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>HC Černí kúň</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0087</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0261</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>TR_S2011_12_00308</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>9</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0087</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0262</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>TR_S2011_12_00309</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>10</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>HC Sokol Kněžice</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Třebíč</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0087</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0263</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>TR_S2011_12_00310</t>
         </is>
       </c>
     </row>
@@ -12186,7 +13172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N100"/>
+  <dimension ref="A1:N102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16767,6 +17753,70 @@
       <c r="A100" t="inlineStr">
         <is>
           <t>II.liga: Západ/Střed/Východ + 8F/QF/SF/finále.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0086</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Liberecký – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0087</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Vysočina – Třebíč</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>REG_VYS</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0078</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
         </is>
       </c>
     </row>
@@ -19892,7 +20942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J230"/>
+  <dimension ref="A1:J251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="10" max="10"/>
@@ -29605,6 +30655,678 @@
       <c r="J230" t="inlineStr">
         <is>
           <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0243</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>TJ Bohemians Praha</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>TJ Bohemians Praha</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>30LIBE</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0244</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>HC Predators Česká Lípa</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>HC Predators Česká Lípa</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>30LIBE</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0245</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>HPH Pokojovice</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>HPH Pokojovice</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0246</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Sokol OKŘÍŠKY</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Sokol OKŘÍŠKY</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0247</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>HC LUKÁŠ B</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>HC LUKÁŠ B</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0248</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Veselý TEAM</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Veselý TEAM</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0249</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>KRHOV</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>KRHOV</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0250</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>HC LUKÁŠ A</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>HC LUKÁŠ A</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0251</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>TJ Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>TJ Sokol Stařeč</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0252</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Hokejový klub – Drakstav</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Hokejový klub – Drakstav</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0253</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>HC Drakstav</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>HC Drakstav</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0254</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>MÁ Jihlava</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>MÁ Jihlava</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0255</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>HC Rantířov</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>HC Rantířov</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0256</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0257</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0258</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>HC Janovice</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>HC Janovice</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0259</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>HC Fan Club Dukla Jihlava</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>HC Fan Club Dukla Jihlava</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0260</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice-Brod</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice-Brod</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0261</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>HC Černí kúň</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>HC Černí kúň</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0262</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>CLUB_S2011_12_0263</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>HC Sokol Kněžice</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>HC Sokol Kněžice</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
         </is>
       </c>
     </row>

--- a/data/S2011_12_FINAL.xlsx
+++ b/data/S2011_12_FINAL.xlsx
@@ -39,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +58,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -81,6 +85,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -94,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -105,6 +114,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -17596,8 +17607,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87"/>
-    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
@@ -17727,7 +17736,6 @@
         </is>
       </c>
     </row>
-    <row r="96"/>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
@@ -34181,7 +34189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -34238,7 +34246,7 @@
           <t>CLUB_S2011_12_0010</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34258,7 +34266,7 @@
           <t>CLUB_S2011_12_0016</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34278,7 +34286,7 @@
           <t>CLUB_S2011_12_0024</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34298,7 +34306,7 @@
           <t>CLUB_S2011_12_0031</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -34318,7 +34326,7 @@
           <t>CLUB_S2011_12_0035</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34338,7 +34346,7 @@
           <t>CLUB_S2011_12_0050</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34358,7 +34366,7 @@
           <t>CLUB_S2011_12_0051</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34378,7 +34386,7 @@
           <t>CLUB_S2011_12_0056</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34398,7 +34406,7 @@
           <t>CLUB_S2011_12_0058</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34418,7 +34426,7 @@
           <t>CLUB_S2011_12_0059</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34438,7 +34446,7 @@
           <t>CLUB_S2011_12_0067</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S2010_11_0252 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -34458,7 +34466,7 @@
           <t>CLUB_S2011_12_0076</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34478,7 +34486,7 @@
           <t>CLUB_S2011_12_0079</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34498,7 +34506,7 @@
           <t>CLUB_S2011_12_0102</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34518,7 +34526,7 @@
           <t>CLUB_S2011_12_0114</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34538,7 +34546,7 @@
           <t>CLUB_S2011_12_0139</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>TBD: city 'SKP Rapid Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34558,7 +34566,7 @@
           <t>CLUB_S2011_12_0148</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34578,7 +34586,7 @@
           <t>CLUB_S2011_12_0162</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -34598,7 +34606,7 @@
           <t>CLUB_S2011_12_0175</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34618,7 +34626,7 @@
           <t>CLUB_S2011_12_0177</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34638,7 +34646,7 @@
           <t>CLUB_S2011_12_0188</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
@@ -34658,7 +34666,7 @@
           <t>CLUB_S2011_12_0193</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34678,7 +34686,7 @@
           <t>CLUB_S2011_12_0195</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34698,7 +34706,7 @@
           <t>CLUB_S2011_12_0203</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -34718,7 +34726,7 @@
           <t>CLUB_S2011_12_0206</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TBD: city 'Závodní hokejové Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34738,7 +34746,7 @@
           <t>CLUB_S2011_12_0210</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
@@ -34758,7 +34766,7 @@
           <t>CLUB_S2011_12_0225</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>TBD: city 'HCM Warrior Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -34778,7 +34786,7 @@
           <t>NODE_S2011_12_0030</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina A'</t>
         </is>
@@ -34798,7 +34806,7 @@
           <t>NODE_S2011_12_0031</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina B'</t>
         </is>
@@ -34818,11 +34826,115 @@
           <t>NODE_S2011_12_0032</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  Skupina C'</t>
         </is>
       </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>KVAL  Skupina C (celostátní) · NODE_S2011_12_0032</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>máme jen účastníky (HC Moravské Budějovice 2005 (JM), HC Orlová (MS)), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>30_Jihomoravský L40 Finále (Jihomoravský kraj) · NODE_S2011_12_0082</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>máme jen účastníky (HCM Warrior Brno loni jak Kometa Úvoz), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>30_Severomoravský L40 Finále (jihozápadní Morava) · NODE_S2011_12_0085</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>máme jen účastníky (HC Rožnov pod Radhoštěm ze Zlínského kraje), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Liberecký – Krajská liga · NODE_S2011_12_0086</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (TJ Bohemians Praha, HC Predators Česká Lípa), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F31"/>

--- a/data/S2011_12_FINAL.xlsx
+++ b/data/S2011_12_FINAL.xlsx
@@ -103,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -116,6 +116,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -12750,7 +12753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13167,6 +13170,74 @@
         </is>
       </c>
       <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0032</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen účastníky (HC Moravské Budějovice 2005 (JM), HC Orlová (MS)), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0082</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen účastníky (HCM Warrior Brno loni jak Kometa Úvoz), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0085</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen účastníky (HC Rožnov pod Radhoštěm ze Zlínského kraje), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0086</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (TJ Bohemians Praha, HC Predators Česká Lípa), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -34846,7 +34917,7 @@
           <t>KVAL  Skupina C (celostátní) · NODE_S2011_12_0032</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>máme jen účastníky (HC Moravské Budějovice 2005 (JM), HC Orlová (MS)), chybí výsledek / odveta  [torzo-audit]</t>
         </is>
@@ -34872,7 +34943,7 @@
           <t>30_Jihomoravský L40 Finále (Jihomoravský kraj) · NODE_S2011_12_0082</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>máme jen účastníky (HCM Warrior Brno loni jak Kometa Úvoz), chybí výsledek / odveta  [torzo-audit]</t>
         </is>
@@ -34898,7 +34969,7 @@
           <t>30_Severomoravský L40 Finále (jihozápadní Morava) · NODE_S2011_12_0085</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>máme jen účastníky (HC Rožnov pod Radhoštěm ze Zlínského kraje), chybí výsledek / odveta  [torzo-audit]</t>
         </is>
@@ -34924,7 +34995,7 @@
           <t>Liberecký – Krajská liga · NODE_S2011_12_0086</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (TJ Bohemians Praha, HC Predators Česká Lípa), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>

--- a/data/S2011_12_FINAL.xlsx
+++ b/data/S2011_12_FINAL.xlsx
@@ -14934,7 +14934,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KVAL  Skupina A</t>
+          <t>KVAL Skupina A</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -14971,7 +14971,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>KVAL  Skupina B</t>
+          <t>KVAL Skupina B</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -15008,7 +15008,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>KVAL  Skupina C</t>
+          <t>KVAL Skupina C</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -15045,7 +15045,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -15092,7 +15092,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -15790,7 +15790,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -15837,7 +15837,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 základní část</t>
+          <t>Středočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -15897,7 +15897,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 Finále</t>
+          <t>Středočeský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -15999,7 +15999,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 základní část</t>
+          <t>Jihočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -16059,7 +16059,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 Finále</t>
+          <t>Jihočeský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40</t>
+          <t>Plzeňský, 4. úroveň</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -16174,7 +16174,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 skupina A</t>
+          <t>Plzeňský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -16221,7 +16221,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 Finále</t>
+          <t>Plzeňský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -16271,7 +16271,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 skupina B</t>
+          <t>Plzeňský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -16318,7 +16318,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 Finále</t>
+          <t>Plzeňský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 skupina C</t>
+          <t>Plzeňský, 4. úroveň, skupina C</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -16415,7 +16415,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 Finále</t>
+          <t>Plzeňský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -16465,7 +16465,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 skupina D</t>
+          <t>Plzeňský, 4. úroveň, skupina D</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -16507,7 +16507,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 Finále</t>
+          <t>Plzeňský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -16557,7 +16557,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30_Ústecký-Karlovarský L40</t>
+          <t>Ústecký-Karlovarský, 4. úroveň</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -16599,7 +16599,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30_Ústecký-Karlovarský L40 základní část</t>
+          <t>Ústecký-Karlovarský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -16654,7 +16654,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30_Ústecký-Karlovarský L40 základní část</t>
+          <t>Ústecký-Karlovarský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -16709,7 +16709,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>30_Ústecký-Karlovarský L40 Finále</t>
+          <t>Ústecký-Karlovarský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -16759,7 +16759,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30_Liberecký L40</t>
+          <t>Liberecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -16806,7 +16806,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30_Hradecký L40</t>
+          <t>Hradecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -16853,7 +16853,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 základní část</t>
+          <t>Hradecký, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -16900,7 +16900,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 skupina A</t>
+          <t>Hradecký, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 skupina B</t>
+          <t>Hradecký, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -16994,7 +16994,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30_Pardubický L40</t>
+          <t>Pardubický, 4. úroveň</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -17041,7 +17041,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 základní část</t>
+          <t>Pardubický, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -17096,7 +17096,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 skupina A</t>
+          <t>Pardubický, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -17138,7 +17138,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 Finále</t>
+          <t>Pardubický, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -17188,7 +17188,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 skupina B</t>
+          <t>Pardubický, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -17230,7 +17230,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 Finále</t>
+          <t>Pardubický, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -17280,7 +17280,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>30_Vysočina L40</t>
+          <t>Vysočina, 4. úroveň</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -17327,7 +17327,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 základní část</t>
+          <t>Jihomoravský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -17434,7 +17434,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 Finále</t>
+          <t>Jihomoravský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -17484,7 +17484,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 Finále</t>
+          <t>Jihomoravský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -17534,7 +17534,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -17581,7 +17581,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 základní část</t>
+          <t>Severomoravský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 Finále</t>
+          <t>Severomoravský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -17678,6 +17678,8 @@
         <v>5</v>
       </c>
     </row>
+    <row r="87"/>
+    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
@@ -17710,7 +17712,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
+          <t>I.ČNHL (12 CZ) + SNHL (12 Slovensko)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -17807,6 +17809,7 @@
         </is>
       </c>
     </row>
+    <row r="96"/>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>

--- a/data/S2011_12_FINAL.xlsx
+++ b/data/S2011_12_FINAL.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -10418,7 +10418,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -10652,7 +10652,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -17678,8 +17678,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87"/>
-    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
@@ -17809,7 +17807,6 @@
         </is>
       </c>
     </row>
-    <row r="96"/>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
@@ -31719,7 +31716,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -31797,7 +31794,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -31875,7 +31872,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -31953,7 +31950,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -32031,7 +32028,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -32109,7 +32106,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -32187,7 +32184,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -32265,7 +32262,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -32343,7 +32340,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -32421,7 +32418,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -32499,7 +32496,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -32582,7 +32579,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -32660,7 +32657,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -32743,7 +32740,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -33677,7 +33674,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -33755,7 +33752,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -33833,7 +33830,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -51487,7 +51484,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -51565,7 +51562,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -51643,7 +51640,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -51721,7 +51718,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -51799,7 +51796,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -51877,7 +51874,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -51955,7 +51952,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -52033,7 +52030,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -52111,7 +52108,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -52189,7 +52186,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -52267,7 +52264,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
